--- a/errori-it.xlsx
+++ b/errori-it.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f.refrigeri\Documents\Documenti Flavio\MicroserviziWeb\micro-tools-suite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73008B3F-17B3-448B-A428-EA34843EC0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76392A08-FD77-4435-AFC4-58362DA79F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B04216D3-A5F7-4351-8370-6B17A231C3D8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B04216D3-A5F7-4351-8370-6B17A231C3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="93">
   <si>
     <t>Modello</t>
   </si>
@@ -860,6 +860,143 @@
 "E12"
 Classificazione: Reset Elettrico Elettronico
 Gravità: Media</t>
+  </si>
+  <si>
+    <t>Xiaomi</t>
+  </si>
+  <si>
+    <t>Nome
+Xiaomi Dual Zone Air Fryer 10L
+Modello
+MAF-D1001
+Colore
+Nero
+Potenza nominale
+2.700 W (1.150 W a sinistra + 1.450 W a destra)
+Tensione nominale
+220-240 V~
+Frequenza nominale
+50-60 Hz
+Capacità nominale
+10 L (3,5 L a sinistra + 6,5 L a destra)</t>
+  </si>
+  <si>
+    <t>MAF-D1001</t>
+  </si>
+  <si>
+    <t>Xiaomi Dual Zone Air Fryer 10L</t>
+  </si>
+  <si>
+    <t>Xiaomi MAF-D1001 Smart Double Stack Air Fryer User Manual - Manuals+</t>
+  </si>
+  <si>
+    <t>MAF-W6051</t>
+  </si>
+  <si>
+    <t>Xiaomi Air Fryer 6,5L</t>
+  </si>
+  <si>
+    <t>Nome del prodotto
+Xiaomi Air Fryer 6,5L
+Modello del prodotto
+MAF-W6051
+Colore del prodotto
+Bianco
+Nero
+Potenza nominale
+1700 W
+Tensione nominale
+220-240 V~
+Frequenza nominale
+50-60 Hz
+Capacità nominale
+6,5 L</t>
+  </si>
+  <si>
+    <t>Troubleshooting - Xiaomi Smart Air Fryer 6,5 User Manual [Page 10] | ManualsLib</t>
+  </si>
+  <si>
+    <t>"La friggitrice ad aria non funziona."
+La friggitrice ad aria non è collegata all'alimentazione; collega il cavo di alimentazione a una presa elettrica con messa a terra. Il cestello non è spinto in posizione; estrai il cestello e spingilo di nuovo in posizione.   
+"E1"
+Il sensore ha un circuito aperto; contatta il team di assistenza post-vendita.  
+ "E2"
+Il sensore ha un cortocircuito; contatta il team di assistenza post-vendita.   
+"La ventola non gira."
+La pala della ventola è bloccata; contatta il team di assistenza post-vendita. Il motore è danneggiato o altri componenti hanno un circuito interrotto; contatta il team di assistenza post-vendita.  
+ "Esce fumo bianco."
+Cottura di ingredienti grassi: quando si friggono ingredienti che contengono più grasso, ci sarà molto fumo, il che è normale. La friggitrice ad aria contiene ancora residui di grasso del programma di cottura precedente; assicurati di pulire la friggitrice ad aria dopo ogni programma di cottura.   
+"Non è possibile inserire agevolmente il cestello nella friggitrice ad aria."
+Troppi ingredienti nel cestello; gli ingredienti nel cestello non possono superare il segno massimo. Il cestello non è inserito correttamente; inserisci correttamente il cestello.</t>
+  </si>
+  <si>
+    <t>"La friggitrice ad aria non funziona."
+La friggitrice ad aria non è collegata all'alimentazione; collega il cavo di alimentazione a una presa elettrica con messa a terra. Il cestello non è spinto in posizione; estrai il cestello e spingilo di nuovo in posizione.
+"E1"
+Il sensore ha un circuito aperto; contatta il team di assistenza post-vendita.
+"E2"
+Il sensore ha un cortocircuito; contatta il team di assistenza post-vendita.
+"La ventola non gira."
+La pala della ventola è bloccata; contatta il team di assistenza post-vendita. Il motore è danneggiato o altri componenti hanno un circuito interrotto; contatta il team di assistenza post-vendita.
+"Esce fumo bianco."
+Cottura di ingredienti grassi: quando si friggono ingredienti che contengono più grasso, ci sarà molto fumo, il che è normale. La friggitrice ad aria contiene ancora residui di grasso del programma di cottura precedente; assicurati di pulire la friggitrice ad aria dopo ogni programma di cottura.
+"Non è possibile inserire agevolmente il cestello nella friggitrice ad aria."
+Troppi ingredienti nel cestello; gli ingredienti nel cestello non possono superare il segno massimo. Il cestello non è inserito correttamente; inserisci correttamente il cestello.
+"La funzione di programmazione non funziona come richiesto."
+Il tempo programmato è troppo breve; il tempo programmato dovrebbe essere più lungo del tempo di cottura. Il tempo programmato non è stato salvato; il tempo programmato deve essere salvato ed eseguito premendo la manopola di controllo.
+"Impossibile connettere il Wi-Fi."
+L'app Mi Home/Xiaomi Home non è all'ultima versione; aggiorna l'app Mi Home/Xiaomi Home all'ultima versione. Il segnale Wi-Fi è debole; spostati in una posizione in cui il segnale sia abbastanza forte.
+"Impossibile connettere la friggitrice ad aria."
+Impossibile connettere il Wi-Fi; controlla se il Wi-Fi è connesso normalmente o ripristina il Wi-Fi per riconnetterti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"La friggitrice ad aria non funziona."
+Classificazione: Controllo Alimentazione / Assemblaggio
+Gravità: Bassa 
+"E1"
+Classificazione: Riparazione Hardware
+Gravità: Alta 
+ "E2"
+Classificazione: Riparazione Hardware
+Gravità: Alta  
+"La ventola non gira."
+Classificazione: Riparazione Hardware
+Gravità: Alta  
+ "Esce fumo bianco."
+Classificazione: Pulizia / Funzionamento Normale
+Gravità: Bassa  
+"Non è possibile inserire agevolmente il cestello nella friggitrice ad aria."
+Classificazione: Errore di Utilizzo / Capacità
+Gravità: Bassa   </t>
+  </si>
+  <si>
+    <t>"La friggitrice ad aria non funziona."
+Classificazione: Controllo Alimentazione / Assemblaggio
+Gravità: Bassa
+"E1"
+Classificazione: Riparazione Hardware
+Gravità: Alta
+"E2"
+Classificazione: Riparazione Hardware
+Gravità: Alta
+"La ventola non gira."
+Classificazione: Riparazione Hardware
+Gravità: Alta
+"Esce fumo bianco."
+Classificazione: Pulizia / Funzionamento Normale
+Gravità: Bassa
+"Non è possibile inserire agevolmente il cestello nella friggitrice ad aria."
+Classificazione: Errore di Utilizzo / Capacità
+Gravità: Bassa
+"La funzione di programmazione non funziona come richiesto."
+Classificazione: Errore Software / Impostazione
+Gravità: Bassa
+"Impossibile connettere il Wi-Fi."
+Classificazione: Errore di Rete / App
+Gravità: Bassa
+"Impossibile connettere la friggitrice ad aria."
+Classificazione: Errore di Rete / App
+Gravità: Bassa</t>
   </si>
 </sst>
 </file>
@@ -912,7 +1049,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -933,9 +1070,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1278,7 +1412,8 @@
     <col min="2" max="3" width="42.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" customWidth="1"/>
     <col min="5" max="6" width="164.85546875" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" style="2" customWidth="1"/>
     <col min="9" max="9" width="62.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1662,8 +1797,53 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="8"/>
+    <row r="15" spans="1:9" ht="360" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" s="7"/>
@@ -1676,8 +1856,10 @@
     <hyperlink ref="B13" r:id="rId4" display="https://cosori.com/collections/air-fryers/products/cosori-9-0-quart-dual-basket-air-fryer" xr:uid="{8EC56DBC-F1F4-4514-A77F-05AAC78611AA}"/>
     <hyperlink ref="B14" r:id="rId5" display="https://cosori.com/collections/air-fryers/products/pro-le-5-0-quart-air-fryer" xr:uid="{D85EA65E-A5F5-4BC1-82C1-CB02345C9CAF}"/>
     <hyperlink ref="H2" r:id="rId6" xr:uid="{22849964-AC6B-4C88-9146-73D0581B39AB}"/>
+    <hyperlink ref="G15" r:id="rId7" display="https://it.manuals.plus/xiaomi/maf-d1001-smart-double-stack-air-fryer-manual" xr:uid="{FCDE6A53-EF24-4F5E-9C1F-4947B1166DAD}"/>
+    <hyperlink ref="G16" r:id="rId8" display="https://www.manualslib.com/manual/3272450/Xiaomi-Smart-Air-Fryer-6-5.html?page=10" xr:uid="{A8CC3A7A-DE43-40B3-9931-C4D21975DDAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/errori-it.xlsx
+++ b/errori-it.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f.refrigeri\Documents\Documenti Flavio\MicroserviziWeb\micro-tools-suite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76392A08-FD77-4435-AFC4-58362DA79F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09063C3B-F90B-4033-BFA0-8893CF0A4A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B04216D3-A5F7-4351-8370-6B17A231C3D8}"/>
+    <workbookView xWindow="30270" yWindow="1470" windowWidth="28800" windowHeight="15345" xr2:uid="{B04216D3-A5F7-4351-8370-6B17A231C3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
